--- a/data/ROSA/test_item_sequence_all_cases.xlsx
+++ b/data/ROSA/test_item_sequence_all_cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victor/Desktop/TestPlaner/WTK_TestPlaner/data/ROSA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WTK_TestPlaner\data\ROSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5316B0D8-4000-0F4E-89BD-5D2770B9FBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E36CAA7-6C5A-4EE0-98BA-49D08720D09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2784" yWindow="3204" windowWidth="14796" windowHeight="8880" firstSheet="13" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Case_01" sheetId="1" r:id="rId1"/>
@@ -46,12 +46,26 @@
     <sheet name="Case_31" sheetId="31" r:id="rId31"/>
     <sheet name="Case_32" sheetId="32" r:id="rId32"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="109">
   <si>
     <t>Convert_ID=1 | Standard=EIA - 19" | Functionality=Functional | Gold_Rail=Yes | Ufit_SoR=Yes | Systems=1</t>
   </si>
@@ -323,48 +337,73 @@
     <t>Convert_ID=22 | Standard=OCP - 21" | Functionality=Functional | Gold_Rail=No | Ufit_SoR=Yes | Systems=2</t>
   </si>
   <si>
+    <t>Convert_ID=24 | Standard=OCP - 21" | Functionality=Functional | Gold_Rail=No | Ufit_SoR=No | Systems=2</t>
+  </si>
+  <si>
+    <t>Convert_ID=25 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=Yes | Ufit_SoR=Yes | Systems=1</t>
+  </si>
+  <si>
+    <t>Convert_ID=26 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=Yes | Ufit_SoR=Yes | Systems=2</t>
+  </si>
+  <si>
+    <t>Convert_ID=27 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=Yes | Ufit_SoR=No | Systems=1</t>
+  </si>
+  <si>
+    <t>Convert_ID=28 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=Yes | Ufit_SoR=No | Systems=2</t>
+  </si>
+  <si>
+    <t>Convert_ID=29 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=No | Ufit_SoR=Yes | Systems=1</t>
+  </si>
+  <si>
+    <t>Convert_ID=30 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=No | Ufit_SoR=Yes | Systems=2</t>
+  </si>
+  <si>
+    <t>Convert_ID=31 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=No | Ufit_SoR=No | Systems=1</t>
+  </si>
+  <si>
+    <t>Convert_ID=32 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=No | Ufit_SoR=No | Systems=2</t>
+  </si>
+  <si>
+    <t>Haha</t>
+  </si>
+  <si>
+    <t>ENG0013791_CHECK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV0102 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SV0106 </t>
+  </si>
+  <si>
+    <t>SV0103</t>
+  </si>
+  <si>
+    <t>ENG0013791_UFIT</t>
+  </si>
+  <si>
+    <t>SV0114</t>
+  </si>
+  <si>
+    <t>SV0118</t>
+  </si>
+  <si>
+    <t>SV0117</t>
+  </si>
+  <si>
     <t>Convert_ID=23 | Standard=OCP - 21" | Functionality=Functional | Gold_Rail=No | Ufit_SoR=No | Systems=1</t>
-  </si>
-  <si>
-    <t>Convert_ID=24 | Standard=OCP - 21" | Functionality=Functional | Gold_Rail=No | Ufit_SoR=No | Systems=2</t>
-  </si>
-  <si>
-    <t>Convert_ID=25 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=Yes | Ufit_SoR=Yes | Systems=1</t>
-  </si>
-  <si>
-    <t>Convert_ID=26 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=Yes | Ufit_SoR=Yes | Systems=2</t>
-  </si>
-  <si>
-    <t>Convert_ID=27 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=Yes | Ufit_SoR=No | Systems=1</t>
-  </si>
-  <si>
-    <t>Convert_ID=28 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=Yes | Ufit_SoR=No | Systems=2</t>
-  </si>
-  <si>
-    <t>Convert_ID=29 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=No | Ufit_SoR=Yes | Systems=1</t>
-  </si>
-  <si>
-    <t>Convert_ID=30 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=No | Ufit_SoR=Yes | Systems=2</t>
-  </si>
-  <si>
-    <t>Convert_ID=31 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=No | Ufit_SoR=No | Systems=1</t>
-  </si>
-  <si>
-    <t>Convert_ID=32 | Standard=OCP - 21" | Functionality=Non-functional | Gold_Rail=No | Ufit_SoR=No | Systems=2</t>
-  </si>
-  <si>
-    <t>Haha</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -374,6 +413,13 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -401,15 +447,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -710,23 +759,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -881,12 +930,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -894,23 +944,23 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1065,17 +1115,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1083,23 +1134,23 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1254,12 +1305,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1267,23 +1319,23 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1438,17 +1490,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1456,23 +1509,23 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1627,12 +1680,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1640,23 +1694,23 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1811,17 +1865,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1829,23 +1884,23 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2000,12 +2055,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2013,23 +2069,33 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="21" width="10" customWidth="1"/>
+    <col min="1" max="1" width="26.875" customWidth="1"/>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="3" max="3" width="21.375" customWidth="1"/>
+    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="23.375" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="18.875" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2184,41 +2250,82 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>107</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2373,12 +2480,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2386,23 +2494,23 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2557,17 +2665,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2575,23 +2684,23 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2746,12 +2855,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2759,23 +2869,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -2930,7 +3040,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -2980,9 +3090,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -3031,6 +3141,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3038,23 +3149,23 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3209,17 +3320,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3227,23 +3339,23 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3398,12 +3510,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3411,23 +3524,23 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3582,17 +3695,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3600,23 +3714,23 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3771,12 +3885,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3784,23 +3899,23 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3955,17 +4070,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3973,23 +4089,23 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -4144,12 +4260,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4157,23 +4274,23 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -4328,17 +4445,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4346,23 +4464,23 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -4517,12 +4635,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4530,23 +4649,23 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -4701,17 +4820,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4719,23 +4839,23 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -4890,12 +5010,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4903,23 +5024,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -5074,12 +5195,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5087,23 +5209,23 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -5258,17 +5380,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5276,23 +5399,23 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -5447,12 +5570,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5460,23 +5584,23 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -5631,17 +5755,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5649,23 +5774,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -5820,17 +5945,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5838,23 +5964,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -6009,12 +6135,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6022,23 +6149,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -6193,17 +6320,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6211,23 +6339,23 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -6382,12 +6510,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6395,23 +6524,23 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AY5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -6566,17 +6695,18 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6584,23 +6714,23 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:AY4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="21" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:51" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:51" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -6755,12 +6885,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/ROSA/test_item_sequence_all_cases.xlsx
+++ b/data/ROSA/test_item_sequence_all_cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WTK_TestPlaner\data\ROSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA6989D-D089-4A7F-9889-4E20C2554777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B68194E-0186-40DF-9CD6-D26A94E433EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="25" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Case_01" sheetId="1" r:id="rId1"/>
@@ -3776,9 +3776,9 @@
   <dimension ref="A1:AY4"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="1" max="1" width="24.25" customWidth="1"/>
+    <col min="2" max="2" width="32.875" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
     <col min="5" max="5" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3951,34 +3951,37 @@
       <c r="A4" t="s">
         <v>53</v>
       </c>
-      <c r="B4" t="s">
-        <v>74</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
       </c>
       <c r="D4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
         <v>75</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>74</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>66</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>67</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>68</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>69</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>70</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>70</v>
       </c>
     </row>
